--- a/docs/enterprise/06-XLSX/candidate/UAT-Master-Script-v1.0.xlsx
+++ b/docs/enterprise/06-XLSX/candidate/UAT-Master-Script-v1.0.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6b04eb69dd154338"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Control" sheetId="2" r:id="R0a4ac3ef6e184080"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" r:id="R0bd6d4d2d2014f67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Cases" sheetId="4" r:id="R8289de2b7eb844fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Loop" sheetId="5" r:id="R84cf584f00d6470b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defects" sheetId="6" r:id="Rb27ba4f98c9a46b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="7" r:id="R28f46e0f510444e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sign-off" sheetId="8" r:id="Rc93c5fdf220b45b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookups" sheetId="9" r:id="R1e86354b200f4048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5cfa977af00646bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Control" sheetId="2" r:id="Re8609fb7f9c74084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" r:id="Rc085f31aad334fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Cases" sheetId="4" r:id="R154891f2f956424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Loop" sheetId="5" r:id="Rebeeaa8856e84222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defects" sheetId="6" r:id="Rfe2d91f5962b4f0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="7" r:id="R554dab85c3a54216"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sign-off" sheetId="8" r:id="Rec63c64ca2094cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookups" sheetId="9" r:id="Rdccb2fc921bf4f69"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -662,8 +662,14 @@
         <x:v>Document ID</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>WF-QA-010-XLSX</x:v>
-      </x:c>
+        <x:v>WF-QA-022-XLSX</x:v>
+      </x:c>
+      <x:c r="C4" s="16"/>
+      <x:c r="D4" s="16"/>
+      <x:c r="E4" s="16"/>
+      <x:c r="F4" s="16"/>
+      <x:c r="G4" s="16"/>
+      <x:c r="H4" s="16"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
@@ -672,6 +678,12 @@
       <x:c r="B5" s="16" t="str">
         <x:v>WS-Sale-App</x:v>
       </x:c>
+      <x:c r="C5" s="16"/>
+      <x:c r="D5" s="16"/>
+      <x:c r="E5" s="16"/>
+      <x:c r="F5" s="16"/>
+      <x:c r="G5" s="16"/>
+      <x:c r="H5" s="16"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
@@ -680,30 +692,54 @@
       <x:c r="B6" s="16" t="str">
         <x:v>World Fert Co., Ltd.</x:v>
       </x:c>
+      <x:c r="C6" s="16"/>
+      <x:c r="D6" s="16"/>
+      <x:c r="E6" s="16"/>
+      <x:c r="F6" s="16"/>
+      <x:c r="G6" s="16"/>
+      <x:c r="H6" s="16"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
-        <x:v>1.0.0</x:v>
-      </x:c>
+        <x:v>1.0.1</x:v>
+      </x:c>
+      <x:c r="C7" s="16"/>
+      <x:c r="D7" s="16"/>
+      <x:c r="E7" s="16"/>
+      <x:c r="F7" s="16"/>
+      <x:c r="G7" s="16"/>
+      <x:c r="H7" s="16"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
         <x:v>Source commit</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>8dc03bd0d6c6bdfc765c6b61158df6f2b1e12301</x:v>
-      </x:c>
+        <x:v>79a10a28e6a2fba9b65dc85101ff8ab6d784b91c</x:v>
+      </x:c>
+      <x:c r="C8" s="16"/>
+      <x:c r="D8" s="16"/>
+      <x:c r="E8" s="16"/>
+      <x:c r="F8" s="16"/>
+      <x:c r="G8" s="16"/>
+      <x:c r="H8" s="16"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
         <x:v>Generated at</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="n">
-        <x:v>46225.84231290509</x:v>
-      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>UTC 2026-07-23T09:59:36.255Z</x:v>
+      </x:c>
+      <x:c r="C9" s="16"/>
+      <x:c r="D9" s="16"/>
+      <x:c r="E9" s="16"/>
+      <x:c r="F9" s="16"/>
+      <x:c r="G9" s="16"/>
+      <x:c r="H9" s="16"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="str">
@@ -712,6 +748,12 @@
       <x:c r="B10" s="16" t="str">
         <x:v>Review / Candidate</x:v>
       </x:c>
+      <x:c r="C10" s="16"/>
+      <x:c r="D10" s="16"/>
+      <x:c r="E10" s="16"/>
+      <x:c r="F10" s="16"/>
+      <x:c r="G10" s="16"/>
+      <x:c r="H10" s="16"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="str">
@@ -720,6 +762,12 @@
       <x:c r="B11" s="16" t="str">
         <x:v>Confidential — Client / Authorized Partner Use Only</x:v>
       </x:c>
+      <x:c r="C11" s="16"/>
+      <x:c r="D11" s="16"/>
+      <x:c r="E11" s="16"/>
+      <x:c r="F11" s="16"/>
+      <x:c r="G11" s="16"/>
+      <x:c r="H11" s="16"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12" t="str">
@@ -728,6 +776,12 @@
       <x:c r="B12" s="16" t="str">
         <x:v>uat-cases.json</x:v>
       </x:c>
+      <x:c r="C12" s="16"/>
+      <x:c r="D12" s="16"/>
+      <x:c r="E12" s="16"/>
+      <x:c r="F12" s="16"/>
+      <x:c r="G12" s="16"/>
+      <x:c r="H12" s="16"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="18" t="str">
@@ -923,6 +977,15 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="B4:H4"/>
+    <x:mergeCell ref="B5:H5"/>
+    <x:mergeCell ref="B6:H6"/>
+    <x:mergeCell ref="B7:H7"/>
+    <x:mergeCell ref="B8:H8"/>
+    <x:mergeCell ref="B9:H9"/>
+    <x:mergeCell ref="B10:H10"/>
+    <x:mergeCell ref="B11:H11"/>
+    <x:mergeCell ref="B12:H12"/>
     <x:mergeCell ref="A14:H14"/>
     <x:mergeCell ref="C15:H15"/>
     <x:mergeCell ref="C16:H16"/>
@@ -1006,13 +1069,13 @@
         <x:v>Application version</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>1.0.0</x:v>
+        <x:v>1.0.1</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
         <x:v>Source commit</x:v>
       </x:c>
       <x:c r="H5" s="16" t="str">
-        <x:v>8dc03bd0d6c6bdfc765c6b61158df6f2b1e12301</x:v>
+        <x:v>79a10a28e6a2fba9b65dc85101ff8ab6d784b91c</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2717,7 +2780,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59719aa437ba43fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6314e7bbe3946e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3685,7 +3748,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c539eaee461452a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R488e26180fda4088"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4493,7 +4556,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref2d320f1e6a4702"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb54d2c68a3746cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
